--- a/TestData/LV_TC2331_TMTC0002485_VerifyTheRolesAvailable.xlsx
+++ b/TestData/LV_TC2331_TMTC0002485_VerifyTheRolesAvailable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE9F7B5-7B8A-4750-AE61-1CB542AB6244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496EFF74-9165-4E14-A91E-6E75B836F11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>StdUser</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>James Craven</t>
+  </si>
+  <si>
+    <t>Project Peloton</t>
   </si>
 </sst>
 </file>
@@ -389,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
@@ -397,7 +400,7 @@
     <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -408,7 +411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -416,18 +419,24 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -435,7 +444,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>5</v>
       </c>

--- a/TestData/LV_TC2331_TMTC0002485_VerifyTheRolesAvailable.xlsx
+++ b/TestData/LV_TC2331_TMTC0002485_VerifyTheRolesAvailable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496EFF74-9165-4E14-A91E-6E75B836F11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97DFA85-6CC7-4BBA-81E4-70F9449F155B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>StdUser</t>
   </si>
@@ -66,6 +66,15 @@
   </si>
   <si>
     <t>Project Peloton</t>
+  </si>
+  <si>
+    <t>Philip Keffer</t>
+  </si>
+  <si>
+    <t>Dylan Hou</t>
+  </si>
+  <si>
+    <t>In- Active</t>
   </si>
 </sst>
 </file>
@@ -89,12 +98,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -109,9 +124,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -392,15 +408,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -410,13 +428,16 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -424,10 +445,13 @@
       <c r="D2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -435,21 +459,30 @@
       <c r="D3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -461,14 +494,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F571702-A1CB-4A5F-B08A-BF5FC34505E8}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -481,17 +514,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA69304C-8CAA-4910-AB61-A1432FD07ADB}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
